--- a/livrables/EDH - Demande enrichissement donnees recette - Formulaires.xlsx
+++ b/livrables/EDH - Demande enrichissement donnees recette - Formulaires.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/anouaraitabdelmalek/Desktop/EDH/LP-Builder/CanvasGenerator/livrables/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0892118C-13D2-1E40-B8EB-CA40733F3A91}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{18A28B14-D7CA-0C4D-B922-0194592543F0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-21380" yWindow="-21000" windowWidth="38400" windowHeight="21000" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="17020" yWindow="-21000" windowWidth="38400" windowHeight="21000" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Lisez-moi" sheetId="1" r:id="rId1"/>
@@ -23,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="201" uniqueCount="172">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="203" uniqueCount="173">
   <si>
     <t>Demande d'enrichissement du jeu de donnees — CRM recette</t>
   </si>
@@ -539,6 +539,9 @@
   </si>
   <si>
     <t>1, 2</t>
+  </si>
+  <si>
+    <t>OP</t>
   </si>
 </sst>
 </file>
@@ -584,7 +587,7 @@
       <name val="Calibri"/>
     </font>
   </fonts>
-  <fills count="7">
+  <fills count="8">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -616,8 +619,14 @@
         <fgColor rgb="FFC6E0B4"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="0" tint="-0.14999847407452621"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="2">
+  <borders count="3">
     <border>
       <left/>
       <right/>
@@ -640,11 +649,22 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFBFBFBF"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFBFBFBF"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="13">
+  <cellXfs count="15">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
@@ -681,6 +701,12 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="6" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1087,7 +1113,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A1:I10"/>
+  <dimension ref="A1:J10"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="5" customWidth="1"/>
@@ -1101,7 +1127,7 @@
     <col min="9" max="9" width="34" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" ht="16" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:10" ht="16" x14ac:dyDescent="0.2">
       <c r="A1" s="4" t="s">
         <v>15</v>
       </c>
@@ -1130,7 +1156,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="2" spans="1:9" ht="64" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:10" ht="64" x14ac:dyDescent="0.2">
       <c r="A2" s="5">
         <v>1</v>
       </c>
@@ -1159,36 +1185,39 @@
         <v>31</v>
       </c>
     </row>
-    <row r="3" spans="1:9" ht="80" x14ac:dyDescent="0.2">
-      <c r="A3" s="5">
+    <row r="3" spans="1:10" ht="80" x14ac:dyDescent="0.2">
+      <c r="A3" s="13">
         <v>2</v>
       </c>
       <c r="B3" s="6" t="s">
         <v>24</v>
       </c>
-      <c r="C3" s="5" t="s">
+      <c r="C3" s="13" t="s">
         <v>32</v>
       </c>
-      <c r="D3" s="5" t="s">
+      <c r="D3" s="13" t="s">
         <v>33</v>
       </c>
-      <c r="E3" s="5" t="s">
+      <c r="E3" s="13" t="s">
         <v>34</v>
       </c>
-      <c r="F3" s="5" t="s">
+      <c r="F3" s="13" t="s">
         <v>35</v>
       </c>
-      <c r="G3" s="5" t="s">
+      <c r="G3" s="13" t="s">
         <v>36</v>
       </c>
-      <c r="H3" s="5" t="s">
+      <c r="H3" s="13" t="s">
         <v>37</v>
       </c>
-      <c r="I3" s="5" t="s">
+      <c r="I3" s="13" t="s">
         <v>38</v>
       </c>
-    </row>
-    <row r="4" spans="1:9" ht="80" x14ac:dyDescent="0.2">
+      <c r="J3" s="14" t="s">
+        <v>172</v>
+      </c>
+    </row>
+    <row r="4" spans="1:10" ht="80" x14ac:dyDescent="0.2">
       <c r="A4" s="5">
         <v>3</v>
       </c>
@@ -1217,7 +1246,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="5" spans="1:9" ht="48" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:10" ht="48" x14ac:dyDescent="0.2">
       <c r="A5" s="5">
         <v>4</v>
       </c>
@@ -1246,36 +1275,39 @@
         <v>51</v>
       </c>
     </row>
-    <row r="6" spans="1:9" ht="64" x14ac:dyDescent="0.2">
-      <c r="A6" s="5">
+    <row r="6" spans="1:10" ht="64" x14ac:dyDescent="0.2">
+      <c r="A6" s="13">
         <v>5</v>
       </c>
       <c r="B6" s="7" t="s">
         <v>39</v>
       </c>
-      <c r="C6" s="5" t="s">
+      <c r="C6" s="13" t="s">
         <v>52</v>
       </c>
-      <c r="D6" s="5" t="s">
+      <c r="D6" s="13" t="s">
         <v>53</v>
       </c>
-      <c r="E6" s="5" t="s">
+      <c r="E6" s="13" t="s">
         <v>54</v>
       </c>
-      <c r="F6" s="5" t="s">
+      <c r="F6" s="13" t="s">
         <v>55</v>
       </c>
-      <c r="G6" s="5" t="s">
+      <c r="G6" s="13" t="s">
         <v>56</v>
       </c>
-      <c r="H6" s="5" t="s">
+      <c r="H6" s="13" t="s">
         <v>57</v>
       </c>
-      <c r="I6" s="5" t="s">
+      <c r="I6" s="13" t="s">
         <v>58</v>
       </c>
-    </row>
-    <row r="7" spans="1:9" ht="64" x14ac:dyDescent="0.2">
+      <c r="J6" s="14" t="s">
+        <v>172</v>
+      </c>
+    </row>
+    <row r="7" spans="1:10" ht="64" x14ac:dyDescent="0.2">
       <c r="A7" s="5">
         <v>6</v>
       </c>
@@ -1304,7 +1336,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="8" spans="1:9" ht="64" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:10" ht="64" x14ac:dyDescent="0.2">
       <c r="A8" s="5">
         <v>7</v>
       </c>
@@ -1333,7 +1365,7 @@
         <v>72</v>
       </c>
     </row>
-    <row r="9" spans="1:9" ht="64" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:10" ht="64" x14ac:dyDescent="0.2">
       <c r="A9" s="5">
         <v>8</v>
       </c>
@@ -1362,7 +1394,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="10" spans="1:9" ht="64" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:10" ht="64" x14ac:dyDescent="0.2">
       <c r="A10" s="5">
         <v>9</v>
       </c>
